--- a/data/nuevos_clientes.xlsx
+++ b/data/nuevos_clientes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D204"/>
+  <dimension ref="A1:D208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1293,7 +1293,7 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1302,16 +1302,16 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2247,7 +2247,7 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -2256,16 +2256,16 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -2274,16 +2274,16 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -2292,16 +2292,16 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -2310,11 +2310,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106">
@@ -2481,7 +2481,7 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -2490,16 +2490,16 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -2508,11 +2508,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="117">
@@ -2697,7 +2697,7 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -2706,16 +2706,16 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -2724,16 +2724,16 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -2760,11 +2760,11 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131">
@@ -2895,7 +2895,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -2904,16 +2904,16 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -2922,11 +2922,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -2967,7 +2967,7 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -2976,16 +2976,16 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -2994,11 +2994,11 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="144">
@@ -3201,7 +3201,7 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -3210,16 +3210,16 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -3228,11 +3228,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157">
@@ -3399,7 +3399,7 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -3417,7 +3417,7 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -3435,7 +3435,7 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -3444,16 +3444,16 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -3462,11 +3462,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170">
@@ -3813,7 +3813,7 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -3822,16 +3822,16 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -3840,11 +3840,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191">
@@ -3885,7 +3885,7 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -3894,16 +3894,16 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -3912,11 +3912,11 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="195">
@@ -4097,6 +4097,78 @@
       </c>
       <c r="D204" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>203</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>206</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
